--- a/data/test_orders_from_sheet.xlsx
+++ b/data/test_orders_from_sheet.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OD337915012166</t>
+          <t>OD337915012166989100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -563,10 +563,10 @@
         <v>284</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>46228</v>
+        <v>46197</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>46231</v>
+        <v>46200</v>
       </c>
       <c r="K2" t="n">
         <v>10</v>
@@ -600,7 +600,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OD337915105120</t>
+          <t>OD337915105120141100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OD337915117555</t>
+          <t>OD337915117555423100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OD337960018546</t>
+          <t>OD337960018546978100</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -749,10 +749,10 @@
         <v>686</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>46229</v>
+        <v>46202</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>46232</v>
+        <v>46205</v>
       </c>
       <c r="K5" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OD337974610559</t>
+          <t>OD337974610559997100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -811,10 +811,10 @@
         <v>645</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>46230</v>
+        <v>46204</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>46233</v>
+        <v>46209</v>
       </c>
       <c r="K6" t="n">
         <v>10</v>
@@ -848,7 +848,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OD337974610559</t>
+          <t>OD337974610559997100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -873,10 +873,10 @@
         <v>645</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>46230</v>
+        <v>46204</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>46233</v>
+        <v>46209</v>
       </c>
       <c r="K7" t="n">
         <v>10</v>
@@ -910,7 +910,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OD337974610559</t>
+          <t>OD337974610559997100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -935,13 +935,13 @@
         <v>645</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OD337974610559</t>
+          <t>OD337974610559997100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -997,10 +997,10 @@
         <v>644</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>46230</v>
+        <v>46204</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>46233</v>
+        <v>46209</v>
       </c>
       <c r="K9" t="n">
         <v>10</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OD337983106511</t>
+          <t>OD337983106511516100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1059,10 +1059,10 @@
         <v>955</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>46229</v>
+        <v>46205</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="K10" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OD337983106511</t>
+          <t>OD337983106511516100</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1121,10 +1121,10 @@
         <v>954</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>46229</v>
+        <v>46205</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="K11" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OD337983703007</t>
+          <t>OD337983703007211100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1183,10 +1183,10 @@
         <v>395</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>46233</v>
+        <v>46205</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>46236</v>
+        <v>46212</v>
       </c>
       <c r="K12" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OD337983703007</t>
+          <t>OD337983703007211100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1245,10 +1245,10 @@
         <v>395</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>46233</v>
+        <v>46205</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>46236</v>
+        <v>46212</v>
       </c>
       <c r="K13" t="n">
         <v>10</v>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OD337983703007</t>
+          <t>OD337983703007211100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1307,10 +1307,10 @@
         <v>396</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>46233</v>
+        <v>46205</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>46236</v>
+        <v>46212</v>
       </c>
       <c r="K14" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OD337983703007</t>
+          <t>OD337983703007211100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1369,10 +1369,10 @@
         <v>396</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>46233</v>
+        <v>46205</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>46236</v>
+        <v>46212</v>
       </c>
       <c r="K15" t="n">
         <v>10</v>
